--- a/output/graficos_regionales_sexo_edad/plot_intra_nacional_e_mat_a_2018_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_nacional_e_mat_a_2018_nacional.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:46</t>
+    <t xml:space="preserve">2026-09-18 09:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
